--- a/edco_knowledge/Edco_Demo_Catalog.xlsx
+++ b/edco_knowledge/Edco_Demo_Catalog.xlsx
@@ -9,19 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Catalog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Catalog'!$A$1:$Q$101</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,34 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F7FB"/>
-        <bgColor rgb="00F2F7FB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -69,34 +46,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,25 +427,6 @@
   </sheetPr>
   <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -572,7907 +516,7750 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>EDCO-NAU-K001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Porthole Frame Keychain</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="n">
         <v>7.88</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" t="n">
         <v>27.99</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" t="n">
         <v>1000</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" t="n">
         <v>8</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>EDCO-SL-C001</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Tropical Fish Charm Set</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" t="n">
         <v>2.23</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="K3" t="n">
         <v>5000</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="L3" t="n">
         <v>12</v>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>EDCO-NAU-R001</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Trident Statement Ring</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Pave CZ</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="n">
         <v>4.79</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" t="n">
         <v>17.95</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" t="n">
         <v>5000</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" t="n">
         <v>12</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>EDCO-NAU-R002</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Ship Wheel Sterling Ring</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" t="n">
         <v>6.63</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" t="n">
         <v>21.99</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" t="n">
         <v>250</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="L5" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>EDCO-DST-D001</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Nassau Conch Shell Pendant</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" t="n">
         <v>33.95</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" t="n">
         <v>500</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>EDCO-WLD-B001</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Elephant March Bracelet</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" t="n">
         <v>9.19</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" t="n">
         <v>25.95</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" t="n">
         <v>1000</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" t="n">
         <v>8</v>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>EDCO-SL-N001</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Sea Shell Layered Necklace</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Pewter</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>3.81</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" t="n">
         <v>13.95</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" t="n">
         <v>1000</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>EDCO-CUS-C001</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Branded Collector Coin</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" t="n">
         <v>9.66</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" t="n">
         <v>28.99</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="K9" t="n">
         <v>1000</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" t="n">
         <v>16</v>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>EDCO-SL-R001</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Pearl Oyster Ring</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>12.98</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" t="n">
         <v>36.95</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" t="n">
         <v>2500</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" t="n">
         <v>8</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>EDCO-NAU-B001</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Anchor Chain Bracelet</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" t="n">
         <v>2.58</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" t="n">
         <v>10.95</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" t="n">
         <v>1000</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>EDCO-DST-R001</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Paradise Island Ring</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>7.2</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" t="n">
         <v>24.99</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="K12" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>EDCO-TRP-E001</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Flamingo Dangle Earrings Deluxe</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" t="n">
         <v>24.95</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" t="n">
         <v>2500</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" t="n">
         <v>8</v>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>EDCO-TRP-D001</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Banana Leaf Pendant</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="n">
         <v>11.8</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" t="n">
         <v>41.95</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K14" t="n">
         <v>1000</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" t="n">
         <v>8</v>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>EDCO-WLD-B002</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Horse Gallop Bracelet</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" t="n">
         <v>8.99</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" t="n">
         <v>31.95</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="K15" t="n">
         <v>500</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="L15" t="n">
         <v>8</v>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>EDCO-TRP-N001</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Surf Wave Necklace</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="n">
         <v>12.95</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" t="n">
         <v>44.99</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="K16" t="n">
         <v>250</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" t="n">
         <v>12</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>EDCO-TRP-B001</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Beach Sunrise Bracelet</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" t="n">
         <v>29.99</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" t="n">
         <v>500</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" t="n">
         <v>10</v>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>EDCO-SL-B001</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Dolphin Pod Charm Bracelet</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="n">
         <v>6.55</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J18" t="n">
         <v>26.99</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="K18" t="n">
         <v>500</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" t="n">
         <v>10</v>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>EDCO-DST-B001</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Cancun Wave Bracelet</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" t="n">
         <v>1.73</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" t="n">
         <v>5.99</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" t="n">
         <v>1000</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>EDCO-CUS-N001</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Personalized Name Necklace</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>7.89</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J20" t="n">
         <v>29.99</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="K20" t="n">
         <v>5000</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" t="n">
         <v>10</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>EDCO-WLD-R001</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Lion Head Ring</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Marquise</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" t="n">
         <v>16.67</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" t="n">
         <v>48.99</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" t="n">
         <v>1000</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" t="n">
         <v>8</v>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>EDCO-DST-N001</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Bahamas Sunset Necklace</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" t="n">
         <v>32.95</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="K22" t="n">
         <v>250</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" t="n">
         <v>8</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>EDCO-SL-P001</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Clownfish Enamel Pin</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" t="n">
         <v>20.65</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" t="n">
         <v>53.99</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" t="n">
         <v>500</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" t="n">
         <v>16</v>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>EDCO-DST-E001</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Jamaica Hummingbird Earrings</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" t="n">
         <v>5.27</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="J24" t="n">
         <v>23.95</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="K24" t="n">
         <v>250</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" t="n">
         <v>8</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>EDCO-DST-R002</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Grand Cayman Stingray Ring</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" t="n">
         <v>21.78</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" t="n">
         <v>73.98999999999999</v>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="K25" t="n">
         <v>1000</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" t="n">
         <v>6</v>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>EDCO-CUS-E001</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Custom Stone Stud Earrings</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" t="n">
         <v>16.31</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="J26" t="n">
         <v>46.99</v>
       </c>
-      <c r="K26" s="4" t="n">
+      <c r="K26" t="n">
         <v>500</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" t="n">
         <v>10</v>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>EDCO-TRP-R001</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Plumeria Blossom Ring</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" t="n">
         <v>4.52</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" t="n">
         <v>17.95</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" t="n">
         <v>1000</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" t="n">
         <v>12</v>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>EDCO-CUS-P001</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Branded Enamel Lapel Pin</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Pave CZ</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Marquise</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" t="n">
         <v>11.14</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="J28" t="n">
         <v>30.95</v>
       </c>
-      <c r="K28" s="4" t="n">
+      <c r="K28" t="n">
         <v>500</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>EDCO-NAU-C001</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Maritime Flag Charm Set</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" t="n">
         <v>10.2</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" t="n">
         <v>26.99</v>
       </c>
-      <c r="K29" s="7" t="n">
+      <c r="K29" t="n">
         <v>2500</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" t="n">
         <v>12</v>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>EDCO-WLD-N001</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Hummingbird Charm Necklace</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="n">
         <v>20.34</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="J30" t="n">
         <v>53.95</v>
       </c>
-      <c r="K30" s="4" t="n">
+      <c r="K30" t="n">
         <v>1000</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" t="n">
         <v>10</v>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>EDCO-WLD-E001</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Peacock Feather Earrings</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" t="n">
         <v>6.9</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" t="n">
         <v>25.99</v>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="K31" t="n">
         <v>1000</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="L31" t="n">
         <v>10</v>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>EDCO-WLD-E002</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Owl Wisdom Earrings</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" t="n">
         <v>8.84</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="J32" t="n">
         <v>28.95</v>
       </c>
-      <c r="K32" s="4" t="n">
+      <c r="K32" t="n">
         <v>500</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" t="n">
         <v>12</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>EDCO-CUS-B001</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Branded Bangle Bracelet</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" t="n">
         <v>12.56</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" t="n">
         <v>31.99</v>
       </c>
-      <c r="K33" s="7" t="n">
+      <c r="K33" t="n">
         <v>500</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L33" t="n">
         <v>12</v>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>EDCO-TRP-E002</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Flamingo Dangle Earrings</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" t="n">
         <v>12.29</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="J34" t="n">
         <v>40.99</v>
       </c>
-      <c r="K34" s="4" t="n">
+      <c r="K34" t="n">
         <v>1000</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" t="n">
         <v>10</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>EDCO-CUS-C002</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Logo Embossed Cuff Links</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" t="n">
         <v>12.97</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" t="n">
         <v>42.99</v>
       </c>
-      <c r="K35" s="7" t="n">
+      <c r="K35" t="n">
         <v>5000</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="L35" t="n">
         <v>10</v>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>EDCO-NAU-N001</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Compass Rose Necklace</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" t="n">
         <v>4.55</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="J36" t="n">
         <v>16.95</v>
       </c>
-      <c r="K36" s="4" t="n">
+      <c r="K36" t="n">
         <v>500</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" t="n">
         <v>12</v>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>EDCO-DST-D002</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Caribbean Map Pendant</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" t="n">
         <v>19</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" t="n">
         <v>53.99</v>
       </c>
-      <c r="K37" s="7" t="n">
+      <c r="K37" t="n">
         <v>2500</v>
       </c>
-      <c r="L37" s="7" t="n">
+      <c r="L37" t="n">
         <v>10</v>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>EDCO-SL-D001</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Shark Tooth Pendant</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" t="n">
         <v>18.32</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="J38" t="n">
         <v>54.95</v>
       </c>
-      <c r="K38" s="4" t="n">
+      <c r="K38" t="n">
         <v>500</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" t="n">
         <v>10</v>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>EDCO-TRP-N002</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Palm Tree Pendant Necklace</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" t="n">
         <v>12.45</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" t="n">
         <v>43.95</v>
       </c>
-      <c r="K39" s="7" t="n">
+      <c r="K39" t="n">
         <v>1000</v>
       </c>
-      <c r="L39" s="7" t="n">
+      <c r="L39" t="n">
         <v>6</v>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>EDCO-SL-B002</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Dolphin Pod Charm Bracelet Deluxe</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" t="n">
         <v>6.68</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="J40" t="n">
         <v>26.95</v>
       </c>
-      <c r="K40" s="4" t="n">
+      <c r="K40" t="n">
         <v>1000</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" t="n">
         <v>10</v>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>EDCO-SL-E001</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Sea Urchin Stud Earrings</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" t="n">
         <v>13.28</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" t="n">
         <v>38.99</v>
       </c>
-      <c r="K41" s="7" t="n">
+      <c r="K41" t="n">
         <v>5000</v>
       </c>
-      <c r="L41" s="7" t="n">
+      <c r="L41" t="n">
         <v>8</v>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>EDCO-TRP-C001</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Tiki Mask Charm</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" t="n">
         <v>12.4</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="J42" t="n">
         <v>36.99</v>
       </c>
-      <c r="K42" s="4" t="n">
+      <c r="K42" t="n">
         <v>1000</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="L42" t="n">
         <v>10</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>EDCO-SL-C002</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Manta Ray Charm</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" t="n">
         <v>14.21</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" t="n">
         <v>39.95</v>
       </c>
-      <c r="K43" s="7" t="n">
+      <c r="K43" t="n">
         <v>2500</v>
       </c>
-      <c r="L43" s="7" t="n">
+      <c r="L43" t="n">
         <v>6</v>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q43" s="5" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>EDCO-DST-C001</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>St Thomas Map Charm</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" t="n">
         <v>11.62</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="J44" t="n">
         <v>34.95</v>
       </c>
-      <c r="K44" s="4" t="n">
+      <c r="K44" t="n">
         <v>1000</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L44" t="n">
         <v>8</v>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>EDCO-TRP-E003</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Mango Drop Earrings</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" t="n">
         <v>26.95</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K45" t="n">
         <v>1000</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="L45" t="n">
         <v>16</v>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P45" s="5" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q45" s="5" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>EDCO-TRP-K001</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Coconut Shell Keychain</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" t="n">
         <v>15.68</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="J46" t="n">
         <v>41.95</v>
       </c>
-      <c r="K46" s="4" t="n">
+      <c r="K46" t="n">
         <v>500</v>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="L46" t="n">
         <v>8</v>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>EDCO-SL-B003</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Stingray Cuff Bracelet</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" t="n">
         <v>20.29</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" t="n">
         <v>66.95</v>
       </c>
-      <c r="K47" s="7" t="n">
+      <c r="K47" t="n">
         <v>250</v>
       </c>
-      <c r="L47" s="7" t="n">
+      <c r="L47" t="n">
         <v>8</v>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q47" s="5" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>EDCO-DST-C002</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Bermuda Triangle Charm</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I48" t="n">
         <v>5.7</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="J48" t="n">
         <v>21.99</v>
       </c>
-      <c r="K48" s="4" t="n">
+      <c r="K48" t="n">
         <v>500</v>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="L48" t="n">
         <v>12</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>EDCO-SL-N002</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Seahorse Pendant Necklace</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" t="n">
         <v>13.53</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" t="n">
         <v>38.99</v>
       </c>
-      <c r="K49" s="7" t="n">
+      <c r="K49" t="n">
         <v>500</v>
       </c>
-      <c r="L49" s="7" t="n">
+      <c r="L49" t="n">
         <v>10</v>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P49" s="5" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q49" s="5" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>EDCO-SL-B004</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Stingray Cuff Bracelet Deluxe</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" t="n">
         <v>8.44</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="J50" t="n">
         <v>22.95</v>
       </c>
-      <c r="K50" s="4" t="n">
+      <c r="K50" t="n">
         <v>1000</v>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="L50" t="n">
         <v>8</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>EDCO-WLD-D001</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Eagle Soar Pendant</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Pave CZ</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I51" t="n">
         <v>15.94</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="J51" t="n">
         <v>54.99</v>
       </c>
-      <c r="K51" s="7" t="n">
+      <c r="K51" t="n">
         <v>1000</v>
       </c>
-      <c r="L51" s="7" t="n">
+      <c r="L51" t="n">
         <v>10</v>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P51" s="5" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q51" s="5" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>EDCO-WLD-R002</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Wolf Howl Ring</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Pewter</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="I52" t="n">
         <v>1.77</v>
       </c>
-      <c r="J52" s="3" t="n">
+      <c r="J52" t="n">
         <v>6.99</v>
       </c>
-      <c r="K52" s="4" t="n">
+      <c r="K52" t="n">
         <v>2500</v>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="L52" t="n">
         <v>12</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>EDCO-NAU-E001</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Nautical Knot Earrings</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I53" s="6" t="n">
+      <c r="I53" t="n">
         <v>13.77</v>
       </c>
-      <c r="J53" s="6" t="n">
+      <c r="J53" t="n">
         <v>46.99</v>
       </c>
-      <c r="K53" s="7" t="n">
+      <c r="K53" t="n">
         <v>1000</v>
       </c>
-      <c r="L53" s="7" t="n">
+      <c r="L53" t="n">
         <v>6</v>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P53" s="5" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q53" s="5" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>EDCO-NAU-B002</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Cruise Ship Charm Bracelet</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="I54" t="n">
         <v>12.49</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="J54" t="n">
         <v>41.95</v>
       </c>
-      <c r="K54" s="4" t="n">
+      <c r="K54" t="n">
         <v>1000</v>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="L54" t="n">
         <v>8</v>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>EDCO-DST-E002</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Alaska Glacier Drop Earrings</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Pewter</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I55" s="6" t="n">
+      <c r="I55" t="n">
         <v>4.44</v>
       </c>
-      <c r="J55" s="6" t="n">
+      <c r="J55" t="n">
         <v>14.95</v>
       </c>
-      <c r="K55" s="7" t="n">
+      <c r="K55" t="n">
         <v>1000</v>
       </c>
-      <c r="L55" s="7" t="n">
+      <c r="L55" t="n">
         <v>10</v>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P55" s="5" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>EDCO-DST-B002</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Mediterranean Tile Bracelet</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I56" s="3" t="n">
+      <c r="I56" t="n">
         <v>18.74</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="J56" t="n">
         <v>62.95</v>
       </c>
-      <c r="K56" s="4" t="n">
+      <c r="K56" t="n">
         <v>2500</v>
       </c>
-      <c r="L56" s="4" t="n">
+      <c r="L56" t="n">
         <v>10</v>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>EDCO-CUS-K001</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Corporate Gift Keychain</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="I57" t="n">
         <v>6.44</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J57" t="n">
         <v>21.99</v>
       </c>
-      <c r="K57" s="7" t="n">
+      <c r="K57" t="n">
         <v>1000</v>
       </c>
-      <c r="L57" s="7" t="n">
+      <c r="L57" t="n">
         <v>6</v>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P57" s="5" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q57" s="5" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>EDCO-SL-P002</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Hammerhead Shark Pin</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Marquise</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="I58" t="n">
         <v>12.5</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="J58" t="n">
         <v>32.99</v>
       </c>
-      <c r="K58" s="4" t="n">
+      <c r="K58" t="n">
         <v>1000</v>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="L58" t="n">
         <v>10</v>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>EDCO-CUS-B002</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Private Label Charm Bracelet</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="I59" t="n">
         <v>17.98</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="J59" t="n">
         <v>53.99</v>
       </c>
-      <c r="K59" s="7" t="n">
+      <c r="K59" t="n">
         <v>2500</v>
       </c>
-      <c r="L59" s="7" t="n">
+      <c r="L59" t="n">
         <v>8</v>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q59" s="5" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>EDCO-SL-E002</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Coral Reef Drop Earrings Deluxe</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Pave CZ</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I60" t="n">
         <v>7.27</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="J60" t="n">
         <v>28.99</v>
       </c>
-      <c r="K60" s="4" t="n">
+      <c r="K60" t="n">
         <v>1000</v>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="L60" t="n">
         <v>10</v>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q60" s="2" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>EDCO-NAU-E002</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Lighthouse Dangle Earrings</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I61" s="6" t="n">
+      <c r="I61" t="n">
         <v>5.22</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J61" t="n">
         <v>16.99</v>
       </c>
-      <c r="K61" s="7" t="n">
+      <c r="K61" t="n">
         <v>250</v>
       </c>
-      <c r="L61" s="7" t="n">
+      <c r="L61" t="n">
         <v>10</v>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P61" s="5" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q61" s="5" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>EDCO-TRP-E004</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Sunset Gradient Earrings</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I62" s="3" t="n">
+      <c r="I62" t="n">
         <v>7.77</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="J62" t="n">
         <v>24.99</v>
       </c>
-      <c r="K62" s="4" t="n">
+      <c r="K62" t="n">
         <v>500</v>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="L62" t="n">
         <v>6</v>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>EDCO-SL-E003</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Coral Reef Drop Earrings</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I63" t="n">
         <v>5.97</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="J63" t="n">
         <v>25.95</v>
       </c>
-      <c r="K63" s="7" t="n">
+      <c r="K63" t="n">
         <v>1000</v>
       </c>
-      <c r="L63" s="7" t="n">
+      <c r="L63" t="n">
         <v>8</v>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q63" s="5" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>EDCO-NAU-K002</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Helm Wheel Keychain</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Pewter</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I64" s="3" t="n">
+      <c r="I64" t="n">
         <v>5.43</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="J64" t="n">
         <v>17.95</v>
       </c>
-      <c r="K64" s="4" t="n">
+      <c r="K64" t="n">
         <v>1000</v>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="L64" t="n">
         <v>12</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q64" s="2" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>EDCO-TRP-P001</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Bird of Paradise Pin</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I65" s="6" t="n">
+      <c r="I65" t="n">
         <v>8.33</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="J65" t="n">
         <v>23.95</v>
       </c>
-      <c r="K65" s="7" t="n">
+      <c r="K65" t="n">
         <v>500</v>
       </c>
-      <c r="L65" s="7" t="n">
+      <c r="L65" t="n">
         <v>6</v>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P65" s="5" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q65" s="5" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>EDCO-SL-R002</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Octopus Wrap Ring</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I66" s="3" t="n">
+      <c r="I66" t="n">
         <v>17.03</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="J66" t="n">
         <v>48.99</v>
       </c>
-      <c r="K66" s="4" t="n">
+      <c r="K66" t="n">
         <v>1000</v>
       </c>
-      <c r="L66" s="4" t="n">
+      <c r="L66" t="n">
         <v>10</v>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q66" s="2" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>EDCO-NAU-D001</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Life Preserver Pendant</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I67" s="6" t="n">
+      <c r="I67" t="n">
         <v>4.03</v>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="J67" t="n">
         <v>15.95</v>
       </c>
-      <c r="K67" s="7" t="n">
+      <c r="K67" t="n">
         <v>1000</v>
       </c>
-      <c r="L67" s="7" t="n">
+      <c r="L67" t="n">
         <v>10</v>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P67" s="5" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q67" s="5" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>EDCO-DST-E003</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Hawaiian Plumeria Earrings</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Marquise</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="I68" t="n">
         <v>11.79</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="J68" t="n">
         <v>35.99</v>
       </c>
-      <c r="K68" s="4" t="n">
+      <c r="K68" t="n">
         <v>500</v>
       </c>
-      <c r="L68" s="4" t="n">
+      <c r="L68" t="n">
         <v>16</v>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>EDCO-DST-P001</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Key West Sunset Pin</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I69" s="6" t="n">
+      <c r="I69" t="n">
         <v>18.66</v>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="J69" t="n">
         <v>63.99</v>
       </c>
-      <c r="K69" s="7" t="n">
+      <c r="K69" t="n">
         <v>500</v>
       </c>
-      <c r="L69" s="7" t="n">
+      <c r="L69" t="n">
         <v>12</v>
       </c>
-      <c r="M69" s="5" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P69" s="5" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q69" s="5" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>EDCO-SL-K001</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Lobster Claw Keychain</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I70" s="3" t="n">
+      <c r="I70" t="n">
         <v>5.58</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="J70" t="n">
         <v>23.99</v>
       </c>
-      <c r="K70" s="4" t="n">
+      <c r="K70" t="n">
         <v>500</v>
       </c>
-      <c r="L70" s="4" t="n">
+      <c r="L70" t="n">
         <v>8</v>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O70" s="2" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>EDCO-DST-N002</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Aruba Divi Tree Necklace</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="I71" t="n">
         <v>20.77</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="J71" t="n">
         <v>59.99</v>
       </c>
-      <c r="K71" s="7" t="n">
+      <c r="K71" t="n">
         <v>500</v>
       </c>
-      <c r="L71" s="7" t="n">
+      <c r="L71" t="n">
         <v>8</v>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P71" s="5" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q71" s="5" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>EDCO-SL-E004</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Sea Urchin Stud Earrings Deluxe</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I72" s="3" t="n">
+      <c r="I72" t="n">
         <v>7.76</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="J72" t="n">
         <v>24.99</v>
       </c>
-      <c r="K72" s="4" t="n">
+      <c r="K72" t="n">
         <v>2500</v>
       </c>
-      <c r="L72" s="4" t="n">
+      <c r="L72" t="n">
         <v>10</v>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>EDCO-SL-B005</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Sand Dollar Bracelet</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I73" s="6" t="n">
+      <c r="I73" t="n">
         <v>5.46</v>
       </c>
-      <c r="J73" s="6" t="n">
+      <c r="J73" t="n">
         <v>21.99</v>
       </c>
-      <c r="K73" s="7" t="n">
+      <c r="K73" t="n">
         <v>1000</v>
       </c>
-      <c r="L73" s="7" t="n">
+      <c r="L73" t="n">
         <v>12</v>
       </c>
-      <c r="M73" s="5" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O73" s="5" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P73" s="5" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q73" s="5" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>EDCO-WLD-D002</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Panda Charm Pendant</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I74" s="3" t="n">
+      <c r="I74" t="n">
         <v>6.71</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="J74" t="n">
         <v>27.95</v>
       </c>
-      <c r="K74" s="4" t="n">
+      <c r="K74" t="n">
         <v>1000</v>
       </c>
-      <c r="L74" s="4" t="n">
+      <c r="L74" t="n">
         <v>10</v>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q74" s="2" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>EDCO-TRP-D002</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Banana Leaf Pendant Deluxe</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I75" s="6" t="n">
+      <c r="I75" t="n">
         <v>12.55</v>
       </c>
-      <c r="J75" s="6" t="n">
+      <c r="J75" t="n">
         <v>35.99</v>
       </c>
-      <c r="K75" s="7" t="n">
+      <c r="K75" t="n">
         <v>1000</v>
       </c>
-      <c r="L75" s="7" t="n">
+      <c r="L75" t="n">
         <v>10</v>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O75" s="5" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P75" s="5" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q75" s="5" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>EDCO-SL-D002</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Manatee Charm Pendant</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I76" s="3" t="n">
+      <c r="I76" t="n">
         <v>1.71</v>
       </c>
-      <c r="J76" s="3" t="n">
+      <c r="J76" t="n">
         <v>6.95</v>
       </c>
-      <c r="K76" s="4" t="n">
+      <c r="K76" t="n">
         <v>5000</v>
       </c>
-      <c r="L76" s="4" t="n">
+      <c r="L76" t="n">
         <v>12</v>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>EDCO-CUS-R001</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Custom Logo Signet Ring</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Marquise</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I77" s="6" t="n">
+      <c r="I77" t="n">
         <v>15.94</v>
       </c>
-      <c r="J77" s="6" t="n">
+      <c r="J77" t="n">
         <v>53.95</v>
       </c>
-      <c r="K77" s="7" t="n">
+      <c r="K77" t="n">
         <v>500</v>
       </c>
-      <c r="L77" s="7" t="n">
+      <c r="L77" t="n">
         <v>10</v>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O77" s="5" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P77" s="5" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>EDCO-DST-K001</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Cozumel Souvenir Keychain</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I78" s="3" t="n">
+      <c r="I78" t="n">
         <v>7.81</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="J78" t="n">
         <v>33.95</v>
       </c>
-      <c r="K78" s="4" t="n">
+      <c r="K78" t="n">
         <v>2500</v>
       </c>
-      <c r="L78" s="4" t="n">
+      <c r="L78" t="n">
         <v>12</v>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q78" s="2" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>EDCO-SL-P003</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Clownfish Enamel Pin Deluxe</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I79" s="6" t="n">
+      <c r="I79" t="n">
         <v>11.27</v>
       </c>
-      <c r="J79" s="6" t="n">
+      <c r="J79" t="n">
         <v>28.95</v>
       </c>
-      <c r="K79" s="7" t="n">
+      <c r="K79" t="n">
         <v>2500</v>
       </c>
-      <c r="L79" s="7" t="n">
+      <c r="L79" t="n">
         <v>8</v>
       </c>
-      <c r="M79" s="5" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O79" s="5" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P79" s="5" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q79" s="5" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>EDCO-NAU-D002</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Anchor Pendant Gold</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I80" s="3" t="n">
+      <c r="I80" t="n">
         <v>8.93</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="J80" t="n">
         <v>25.99</v>
       </c>
-      <c r="K80" s="4" t="n">
+      <c r="K80" t="n">
         <v>1000</v>
       </c>
-      <c r="L80" s="4" t="n">
+      <c r="L80" t="n">
         <v>8</v>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q80" s="2" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>EDCO-SL-R003</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Sea Turtle Sterling Ring</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I81" s="6" t="n">
+      <c r="I81" t="n">
         <v>4.67</v>
       </c>
-      <c r="J81" s="6" t="n">
+      <c r="J81" t="n">
         <v>17.95</v>
       </c>
-      <c r="K81" s="7" t="n">
+      <c r="K81" t="n">
         <v>1000</v>
       </c>
-      <c r="L81" s="7" t="n">
+      <c r="L81" t="n">
         <v>10</v>
       </c>
-      <c r="M81" s="5" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O81" s="5" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P81" s="5" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q81" s="5" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>EDCO-NAU-R003</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Wave Crest Ring</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Pave CZ</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I82" s="3" t="n">
+      <c r="I82" t="n">
         <v>16.26</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="J82" t="n">
         <v>46.99</v>
       </c>
-      <c r="K82" s="4" t="n">
+      <c r="K82" t="n">
         <v>500</v>
       </c>
-      <c r="L82" s="4" t="n">
+      <c r="L82" t="n">
         <v>10</v>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Electroform</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>EDCO-SL-C003</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Manta Ray Charm Deluxe</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Oval</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I83" s="6" t="n">
+      <c r="I83" t="n">
         <v>5.44</v>
       </c>
-      <c r="J83" s="6" t="n">
+      <c r="J83" t="n">
         <v>18.95</v>
       </c>
-      <c r="K83" s="7" t="n">
+      <c r="K83" t="n">
         <v>1000</v>
       </c>
-      <c r="L83" s="7" t="n">
+      <c r="L83" t="n">
         <v>8</v>
       </c>
-      <c r="M83" s="5" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O83" s="5" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P83" s="5" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q83" s="5" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>EDCO-TRP-B002</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Tropical Leaf Cuff Bracelet</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I84" s="3" t="n">
+      <c r="I84" t="n">
         <v>6.19</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="J84" t="n">
         <v>19.95</v>
       </c>
-      <c r="K84" s="4" t="n">
+      <c r="K84" t="n">
         <v>1000</v>
       </c>
-      <c r="L84" s="4" t="n">
+      <c r="L84" t="n">
         <v>8</v>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O84" s="2" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q84" s="2" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>EDCO-NAU-E003</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Nautical Star Stud Earrings</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I85" s="6" t="n">
+      <c r="I85" t="n">
         <v>21.06</v>
       </c>
-      <c r="J85" s="6" t="n">
+      <c r="J85" t="n">
         <v>65.95</v>
       </c>
-      <c r="K85" s="7" t="n">
+      <c r="K85" t="n">
         <v>1000</v>
       </c>
-      <c r="L85" s="7" t="n">
+      <c r="L85" t="n">
         <v>8</v>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N85" s="5" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O85" s="5" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P85" s="5" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q85" s="5" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>EDCO-TRP-R002</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Hibiscus Flower Ring</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I86" s="3" t="n">
+      <c r="I86" t="n">
         <v>6.49</v>
       </c>
-      <c r="J86" s="3" t="n">
+      <c r="J86" t="n">
         <v>23.99</v>
       </c>
-      <c r="K86" s="4" t="n">
+      <c r="K86" t="n">
         <v>2500</v>
       </c>
-      <c r="L86" s="4" t="n">
+      <c r="L86" t="n">
         <v>10</v>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q86" s="2" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>EDCO-WLD-E003</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Butterfly Wing Earrings</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I87" s="6" t="n">
+      <c r="I87" t="n">
         <v>19.9</v>
       </c>
-      <c r="J87" s="6" t="n">
+      <c r="J87" t="n">
         <v>57.95</v>
       </c>
-      <c r="K87" s="7" t="n">
+      <c r="K87" t="n">
         <v>500</v>
       </c>
-      <c r="L87" s="7" t="n">
+      <c r="L87" t="n">
         <v>10</v>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N87" s="5" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O87" s="5" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>Bulk</t>
         </is>
       </c>
-      <c r="P87" s="5" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q87" s="5" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>EDCO-CUS-D001</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Custom Engraved Pendant</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Custom/Private Label</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I88" s="3" t="n">
+      <c r="I88" t="n">
         <v>7.23</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="J88" t="n">
         <v>25.95</v>
       </c>
-      <c r="K88" s="4" t="n">
+      <c r="K88" t="n">
         <v>2500</v>
       </c>
-      <c r="L88" s="4" t="n">
+      <c r="L88" t="n">
         <v>10</v>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>Lifetime</t>
         </is>
       </c>
-      <c r="Q88" s="2" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>EDCO-NAU-B003</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Rope Knot Bangle</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I89" s="6" t="n">
+      <c r="I89" t="n">
         <v>14.39</v>
       </c>
-      <c r="J89" s="6" t="n">
+      <c r="J89" t="n">
         <v>42.95</v>
       </c>
-      <c r="K89" s="7" t="n">
+      <c r="K89" t="n">
         <v>1000</v>
       </c>
-      <c r="L89" s="7" t="n">
+      <c r="L89" t="n">
         <v>8</v>
       </c>
-      <c r="M89" s="5" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O89" s="5" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P89" s="5" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q89" s="5" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>EDCO-WLD-K001</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Bear Claw Keychain</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Pearl</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I90" s="3" t="n">
+      <c r="I90" t="n">
         <v>6.58</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="J90" t="n">
         <v>23.95</v>
       </c>
-      <c r="K90" s="4" t="n">
+      <c r="K90" t="n">
         <v>500</v>
       </c>
-      <c r="L90" s="4" t="n">
+      <c r="L90" t="n">
         <v>8</v>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P90" s="2" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q90" s="2" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>EDCO-SL-C004</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Tropical Fish Charm Set Deluxe</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Charm</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I91" s="6" t="n">
+      <c r="I91" t="n">
         <v>10.15</v>
       </c>
-      <c r="J91" s="6" t="n">
+      <c r="J91" t="n">
         <v>32.95</v>
       </c>
-      <c r="K91" s="7" t="n">
+      <c r="K91" t="n">
         <v>500</v>
       </c>
-      <c r="L91" s="7" t="n">
+      <c r="L91" t="n">
         <v>10</v>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O91" s="5" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P91" s="5" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q91" s="5" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>EDCO-WLD-R003</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Tiger Eye Statement Ring</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Ring</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Colored Stone</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Antique</t>
         </is>
       </c>
-      <c r="I92" s="3" t="n">
+      <c r="I92" t="n">
         <v>6.77</v>
       </c>
-      <c r="J92" s="3" t="n">
+      <c r="J92" t="n">
         <v>21.95</v>
       </c>
-      <c r="K92" s="4" t="n">
+      <c r="K92" t="n">
         <v>2500</v>
       </c>
-      <c r="L92" s="4" t="n">
+      <c r="L92" t="n">
         <v>10</v>
       </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O92" s="2" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>Velvet Pouch</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>EDCO-TRP-P002</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Parrot Enamel Pin</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I93" s="6" t="n">
+      <c r="I93" t="n">
         <v>11.14</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J93" t="n">
         <v>31.95</v>
       </c>
-      <c r="K93" s="7" t="n">
+      <c r="K93" t="n">
         <v>500</v>
       </c>
-      <c r="L93" s="7" t="n">
+      <c r="L93" t="n">
         <v>8</v>
       </c>
-      <c r="M93" s="5" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N93" s="5" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O93" s="5" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P93" s="5" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q93" s="5" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>EDCO-NAU-N002</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Sailboat Charm Necklace</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Necklace</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I94" t="n">
         <v>6.6</v>
       </c>
-      <c r="J94" s="3" t="n">
+      <c r="J94" t="n">
         <v>21.95</v>
       </c>
-      <c r="K94" s="4" t="n">
+      <c r="K94" t="n">
         <v>1000</v>
       </c>
-      <c r="L94" s="4" t="n">
+      <c r="L94" t="n">
         <v>12</v>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>EDCO-NAU-P001</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Captains Wheel Pin</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
         <is>
           <t>Two-Tone</t>
         </is>
       </c>
-      <c r="I95" s="6" t="n">
+      <c r="I95" t="n">
         <v>5.93</v>
       </c>
-      <c r="J95" s="6" t="n">
+      <c r="J95" t="n">
         <v>25.99</v>
       </c>
-      <c r="K95" s="7" t="n">
+      <c r="K95" t="n">
         <v>5000</v>
       </c>
-      <c r="L95" s="7" t="n">
+      <c r="L95" t="n">
         <v>8</v>
       </c>
-      <c r="M95" s="5" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="N95" s="5" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O95" s="5" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P95" s="5" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q95" s="5" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>EDCO-NAU-K003</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Helm Wheel Keychain Deluxe</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Nautical</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Keychain</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I96" t="n">
         <v>6.79</v>
       </c>
-      <c r="J96" s="3" t="n">
+      <c r="J96" t="n">
         <v>26.95</v>
       </c>
-      <c r="K96" s="4" t="n">
+      <c r="K96" t="n">
         <v>1000</v>
       </c>
-      <c r="L96" s="4" t="n">
+      <c r="L96" t="n">
         <v>6</v>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O96" s="2" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>EDCO-SL-E005</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Starfish Stud Earrings</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Rhodium Plate</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Abalone</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>Brushed</t>
         </is>
       </c>
-      <c r="I97" s="6" t="n">
+      <c r="I97" t="n">
         <v>14.76</v>
       </c>
-      <c r="J97" s="6" t="n">
+      <c r="J97" t="n">
         <v>48.99</v>
       </c>
-      <c r="K97" s="7" t="n">
+      <c r="K97" t="n">
         <v>1000</v>
       </c>
-      <c r="L97" s="7" t="n">
+      <c r="L97" t="n">
         <v>12</v>
       </c>
-      <c r="M97" s="5" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N97" s="5" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>Stamped</t>
         </is>
       </c>
-      <c r="O97" s="5" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P97" s="5" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q97" s="5" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>EDCO-SL-D003</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Whale Tail Pendant</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Sterling Silver</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Pear</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I98" s="3" t="n">
+      <c r="I98" t="n">
         <v>12.56</v>
       </c>
-      <c r="J98" s="3" t="n">
+      <c r="J98" t="n">
         <v>34.95</v>
       </c>
-      <c r="K98" s="4" t="n">
+      <c r="K98" t="n">
         <v>1000</v>
       </c>
-      <c r="L98" s="4" t="n">
+      <c r="L98" t="n">
         <v>8</v>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>Gift Box</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>EDCO-TRP-B003</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Pineapple Charm Bracelet</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Tropical</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Bracelet</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Pave CZ</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I99" s="6" t="n">
+      <c r="I99" t="n">
         <v>14.68</v>
       </c>
-      <c r="J99" s="6" t="n">
+      <c r="J99" t="n">
         <v>46.95</v>
       </c>
-      <c r="K99" s="7" t="n">
+      <c r="K99" t="n">
         <v>250</v>
       </c>
-      <c r="L99" s="7" t="n">
+      <c r="L99" t="n">
         <v>10</v>
       </c>
-      <c r="M99" s="5" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N99" s="5" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>Die Cast</t>
         </is>
       </c>
-      <c r="O99" s="5" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>Branded Display Card</t>
         </is>
       </c>
-      <c r="P99" s="5" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q99" s="5" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>EDCO-WLD-P001</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Giraffe Silhouette Pin</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Wildlife</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Brass</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Pave CZ</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Matte</t>
         </is>
       </c>
-      <c r="I100" s="3" t="n">
+      <c r="I100" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="J100" s="3" t="n">
+      <c r="J100" t="n">
         <v>26.99</v>
       </c>
-      <c r="K100" s="4" t="n">
+      <c r="K100" t="n">
         <v>1000</v>
       </c>
-      <c r="L100" s="4" t="n">
+      <c r="L100" t="n">
         <v>6</v>
       </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>Lost Wax Cast</t>
         </is>
       </c>
-      <c r="O100" s="2" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>EDCO-SL-E006</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Jellyfish Dangle Earrings</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Sea Life</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Earring</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Gold Electroplate</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Cushion</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="I101" s="6" t="n">
+      <c r="I101" t="n">
         <v>12.11</v>
       </c>
-      <c r="J101" s="6" t="n">
+      <c r="J101" t="n">
         <v>35.95</v>
       </c>
-      <c r="K101" s="7" t="n">
+      <c r="K101" t="n">
         <v>500</v>
       </c>
-      <c r="L101" s="7" t="n">
+      <c r="L101" t="n">
         <v>8</v>
       </c>
-      <c r="M101" s="5" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="N101" s="5" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>Hand Assembled</t>
         </is>
       </c>
-      <c r="O101" s="5" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>Blister Card</t>
         </is>
       </c>
-      <c r="P101" s="5" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="Q101" s="5" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>